--- a/technical_assessment_by_job/questions/terraform_questions.xlsx
+++ b/technical_assessment_by_job/questions/terraform_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai_ws\technical_assessment_by_job\questions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_openai\codex_projects\technical_assessment_by_job\questions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DDAD179-10F4-4E80-A678-2831EBFCB60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6145164C-EEAF-43D0-8CB6-8D7159D669EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2D37F685-2502-4A38-84D9-569A1400D5DB}"/>
   </bookViews>
@@ -35,10 +35,620 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="199">
+  <si>
+    <t>What is Terraform?</t>
+  </si>
+  <si>
+    <t>Terraform is an open-source Infrastructure as Code (IaC) tool created by HashiCorp. It allows users to define and provision data center infrastructure using a high-level configuration language known as HashiCorp Configuration Language (HCL).</t>
+  </si>
+  <si>
+    <t>What is Infrastructure as Code (IaC)?</t>
+  </si>
+  <si>
+    <t>IaC is the managing and provisioning of infrastructure through code instead of through manual processes. It allows for version control, consistency, and automation in infrastructure management.</t>
+  </si>
+  <si>
+    <t>What is HCL?</t>
+  </si>
+  <si>
+    <t>HCL stands for HashiCorp Configuration Language. It is designed to be human-readable and machine-friendly, used specifically for defining infrastructure in Terraform.</t>
+  </si>
+  <si>
+    <t>What is a Terraform Provider?</t>
+  </si>
+  <si>
+    <t>A provider is a plugin that Terraform uses to interact with cloud providers, SaaS providers, and other APIs (e.g., AWS, Azure, GCP, Kubernetes).</t>
+  </si>
+  <si>
+    <t>What is Terraform State?</t>
+  </si>
+  <si>
+    <t>Terraform state is a file (terraform.tfstate) that keeps track of the resources created by your configuration and maps them to real-world resources.</t>
+  </si>
+  <si>
+    <t>What are the core commands in Terraform?</t>
+  </si>
+  <si>
+    <t>1. terraform init: Initializes the directory. 2. terraform plan: Previews changes. 3. terraform apply: Executes the changes. 4. terraform destroy: Removes all managed resources.</t>
+  </si>
+  <si>
+    <t>What is Terraform Init?</t>
+  </si>
+  <si>
+    <t>It is the first command to run. It initializes the working directory, downloads provider plugins, and sets up the backend for state storage.</t>
+  </si>
+  <si>
+    <t>What is Terraform Plan?</t>
+  </si>
+  <si>
+    <t>It creates an execution plan, showing what actions Terraform will take (create, update, or delete) to reach the desired state defined in the configuration files.</t>
+  </si>
+  <si>
+    <t>What is Terraform Apply?</t>
+  </si>
+  <si>
+    <t>It applies the changes required to reach the desired state of the configuration. By default, it prompts for confirmation before proceeding.</t>
+  </si>
+  <si>
+    <t>What is Terraform Destroy?</t>
+  </si>
+  <si>
+    <t>It is used to delete all the resources managed by the current Terraform configuration.</t>
+  </si>
+  <si>
+    <t>What is a Terraform Module?</t>
+  </si>
+  <si>
+    <t>A module is a container for multiple resources that are used together. It allows for code reusability and better organization of infrastructure.</t>
+  </si>
+  <si>
+    <t>What are Variables in Terraform?</t>
+  </si>
+  <si>
+    <t>Input variables serve as parameters for a Terraform module, allowing you to customize aspects of the infrastructure without altering the main code.</t>
+  </si>
+  <si>
+    <t>What are Output Values?</t>
+  </si>
+  <si>
+    <t>Output values are like return values for a Terraform module. They allow you to share information about your infrastructure (like an IP address) with other configurations.</t>
+  </si>
+  <si>
+    <t>What is a 'Resource' block?</t>
+  </si>
+  <si>
+    <t>A resource block describes one or more infrastructure objects, such as virtual networks or compute instances.</t>
+  </si>
+  <si>
+    <t>What is a 'Data' block?</t>
+  </si>
+  <si>
+    <t>Data blocks allow Terraform to use information defined outside of Terraform, or defined by another separate Terraform configuration.</t>
+  </si>
+  <si>
+    <t>What is a Remote Backend?</t>
+  </si>
+  <si>
+    <t>A remote backend stores the Terraform state file in a remote, shared location (like AWS S3 or HashiCorp Cloud) to allow team collaboration and locking.</t>
+  </si>
+  <si>
+    <t>What is State Locking?</t>
+  </si>
+  <si>
+    <t>State locking prevents multiple users from running Terraform at the same time on the same state file, which could lead to corruption or data loss.</t>
+  </si>
+  <si>
+    <t>What is a Terraform Workspace?</t>
+  </si>
+  <si>
+    <t>Workspaces allow you to manage multiple distinct states of a single configuration on the same backend. Useful for managing dev, stage, and prod environments.</t>
+  </si>
+  <si>
+    <t>What is 'terraform refresh'?</t>
+  </si>
+  <si>
+    <t>It updates the state file with the real-world infrastructure status. It doesn't modify infrastructure but ensures the state reflects reality.</t>
+  </si>
+  <si>
+    <t>What is 'terraform validate'?</t>
+  </si>
+  <si>
+    <t>It checks whether a configuration is syntactically valid and internally consistent.</t>
+  </si>
+  <si>
+    <t>What is 'terraform fmt'?</t>
+  </si>
+  <si>
+    <t>It is used to rewrite Terraform configuration files to a canonical format and style for readability.</t>
+  </si>
+  <si>
+    <t>What is a Terraform Provisioner?</t>
+  </si>
+  <si>
+    <t>Provisioners are used to execute scripts or shell commands on a local or remote machine as part of resource creation or destruction (e.g., local-exec, remote-exec).</t>
+  </si>
+  <si>
+    <t>What are 'Implicit' vs 'Explicit' dependencies?</t>
+  </si>
+  <si>
+    <t>Implicit dependencies are automatically handled by Terraform via attribute references. Explicit dependencies are manually defined using the 'depends_on' argument.</t>
+  </si>
+  <si>
+    <t>What is Terraform Cloud?</t>
+  </si>
+  <si>
+    <t>A managed service that offers a collaborative environment for teams to use Terraform, providing remote state management, VCS integration, and RBAC.</t>
+  </si>
+  <si>
+    <t>What is Terraform Sentinel?</t>
+  </si>
+  <si>
+    <t>Sentinel is a policy-as-code framework used to enforce fine-grained, logic-based policy decisions (e.g., ensuring all S3 buckets are private).</t>
+  </si>
+  <si>
+    <t>What is a 'Taint' command?</t>
+  </si>
+  <si>
+    <t>The 'terraform taint' command (deprecated in favor of 'terraform apply -replace') marks a resource for recreation during the next apply.</t>
+  </si>
+  <si>
+    <t>How do you handle secrets in Terraform?</t>
+  </si>
+  <si>
+    <t>Use environment variables, encrypted files, or integration with secret managers like HashiCorp Vault, AWS Secrets Manager, or Azure Key Vault.</t>
+  </si>
+  <si>
+    <t>What is the 'Graph' command?</t>
+  </si>
+  <si>
+    <t>The 'terraform graph' command generates a visual representation of the configuration or execution plan in DOT format.</t>
+  </si>
+  <si>
+    <t>What is 'null_resource'?</t>
+  </si>
+  <si>
+    <t>A resource that does nothing. It is used to trigger provisioners or to coordinate complex dependencies without creating a real infrastructure object.</t>
+  </si>
+  <si>
+    <t>What is a Multi-Cloud deployment?</t>
+  </si>
+  <si>
+    <t>Provisioning infrastructure across multiple cloud providers (e.g., AWS and Azure) within the same Terraform configuration.</t>
+  </si>
+  <si>
+    <t>What is the difference between Terraform and Ansible?</t>
+  </si>
+  <si>
+    <t>Terraform is primarily an infrastructure provisioning tool (declarative), while Ansible is primarily a configuration management tool (procedural).</t>
+  </si>
+  <si>
+    <t>What is 'state migration'?</t>
+  </si>
+  <si>
+    <t>The process of moving a state file from one backend to another (e.g., moving from local disk to an S3 bucket).</t>
+  </si>
+  <si>
+    <t>What is 'terraform import'?</t>
+  </si>
+  <si>
+    <t>It allows you to bring existing infrastructure resources under Terraform management by mapping them to a resource block in your code.</t>
+  </si>
+  <si>
+    <t>What are Lifecycle Rules?</t>
+  </si>
+  <si>
+    <t>Special arguments (create_before_destroy, prevent_destroy, ignore_changes) that control how Terraform treats specific resources during updates.</t>
+  </si>
+  <si>
+    <t>What is a Module Registry?</t>
+  </si>
+  <si>
+    <t>A repository for sharing Terraform modules. There is a public registry (registry.terraform.io) and private registries for enterprises.</t>
+  </si>
+  <si>
+    <t>What are 'Dynamic Blocks'?</t>
+  </si>
+  <si>
+    <t>They allow you to dynamically construct multiple nested blocks within a resource based on a list or map variable.</t>
+  </si>
+  <si>
+    <t>Explain the 'lookup' function.</t>
+  </si>
+  <si>
+    <t>It retrieves a value from a map given a specific key. If the key doesn't exist, it can return a default value.</t>
+  </si>
+  <si>
+    <t>Explain the 'element' function.</t>
+  </si>
+  <si>
+    <t>It retrieves a single element from a list at a given index.</t>
+  </si>
+  <si>
+    <t>How does Terraform handle drift?</t>
+  </si>
+  <si>
+    <t>Terraform identifies drift (manual changes made outside of Terraform) during the plan/apply phase by comparing the current state with the real-world infrastructure.</t>
+  </si>
+  <si>
+    <t>What is 'Terraform Console'?</t>
+  </si>
+  <si>
+    <t>An interactive command-line interface for evaluating expressions and testing HCL functions and variables.</t>
+  </si>
+  <si>
+    <t>What is the 'locals' block?</t>
+  </si>
+  <si>
+    <t>Locals are like temporary variables within a module to simplify repetitive expressions and improve readability.</t>
+  </si>
+  <si>
+    <t>How can you upgrade Terraform versions?</t>
+  </si>
+  <si>
+    <t>By updating the Terraform binary and then running 'terraform init -upgrade' to update providers and checking for breaking syntax changes.</t>
+  </si>
+  <si>
+    <t>What are 'Count' and 'ForEach'?</t>
+  </si>
+  <si>
+    <t>Both are used to create multiple instances of a resource. 'Count' uses an index, while 'ForEach' uses a map or set of strings.</t>
+  </si>
+  <si>
+    <t>What is the purpose of 'terraform.tfvars'?</t>
+  </si>
+  <si>
+    <t>It is a file used to automatically load variable values into your configuration without passing them via the command line.</t>
+  </si>
+  <si>
+    <t>What is 'backend initialization'?</t>
+  </si>
+  <si>
+    <t>The process where Terraform configures where the state file will be stored during 'terraform init'.</t>
+  </si>
+  <si>
+    <t>What are 'Sensitive' variables?</t>
+  </si>
+  <si>
+    <t>Variables marked as 'sensitive = true' to prevent their values from being displayed in the console output or logs.</t>
+  </si>
+  <si>
+    <t>What is 'Terraform Enterprise'?</t>
+  </si>
+  <si>
+    <t>The self-hosted version of Terraform Cloud, designed for large organizations requiring advanced security and compliance features.</t>
+  </si>
+  <si>
+    <t>What is 'Provider Versioning'?</t>
+  </si>
+  <si>
+    <t>Specifying the exact version or range of versions of a provider plugin to ensure compatibility and stability.</t>
+  </si>
+  <si>
+    <t>What is an 'Alias' in a provider?</t>
+  </si>
+  <si>
+    <t>Allows you to define multiple configurations for the same provider, such as using different regions within a single AWS account.</t>
+  </si>
+  <si>
+    <t>What is 'target' in terraform apply?</t>
+  </si>
+  <si>
+    <t>The '-target' flag allows you to apply changes to a specific resource or module rather than the entire configuration (used for troubleshooting).</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Which command is used to check the version of Terraform?</t>
+  </si>
+  <si>
+    <t>terraform -version</t>
+  </si>
+  <si>
+    <t>What is the name of the default state file in Terraform?</t>
+  </si>
+  <si>
+    <t>terraform.tfstate</t>
+  </si>
+  <si>
+    <t>Which command is used to initialize the working directory containing Terraform configuration files?</t>
+  </si>
+  <si>
+    <t>terraform init</t>
+  </si>
+  <si>
+    <t>True or False: Terraform can only be used with AWS.</t>
+  </si>
+  <si>
+    <t>False. Terraform supports multiple providers like Azure, GCP, Kubernetes, and more.</t>
+  </si>
+  <si>
+    <t>What is the purpose of the 'terraform plan' command?</t>
+  </si>
+  <si>
+    <t>It creates an execution plan, letting you preview changes before applying them.</t>
+  </si>
+  <si>
+    <t>Which file extension is used for Terraform configuration files?</t>
+  </si>
+  <si>
+    <t>.tf (or .tf.json for JSON format).</t>
+  </si>
+  <si>
+    <t>What does the 'terraform apply' command do?</t>
+  </si>
+  <si>
+    <t>It executes the actions proposed in a Terraform plan to reach the desired state of the configuration.</t>
+  </si>
+  <si>
+    <t>Which command is used to remove all resources managed by your Terraform project?</t>
+  </si>
+  <si>
+    <t>terraform destroy</t>
+  </si>
+  <si>
+    <t>A provider is a plugin that Terraform uses to translate HCL code into API calls for specific platforms (e.g., AWS, GitHub).</t>
+  </si>
+  <si>
+    <t>Where does Terraform download provider plugins during initialization?</t>
+  </si>
+  <si>
+    <t>Into the .terraform directory within the project folder.</t>
+  </si>
+  <si>
+    <t>What is 'Terraform State' used for?</t>
+  </si>
+  <si>
+    <t>It maps real-world resources to your configuration, keeps track of metadata, and improves performance for large infrastructures.</t>
+  </si>
+  <si>
+    <t>Which command ensures your configuration files are formatted according to Terraform standards?</t>
+  </si>
+  <si>
+    <t>terraform fmt</t>
+  </si>
+  <si>
+    <t>What is the purpose of the 'terraform validate' command?</t>
+  </si>
+  <si>
+    <t>To check if a configuration is syntactically valid and internally consistent.</t>
+  </si>
+  <si>
+    <t>How do you define an input variable in Terraform?</t>
+  </si>
+  <si>
+    <t>Using the 'variable' block.</t>
+  </si>
+  <si>
+    <t>Which block is used to fetch data from an external source or existing infrastructure?</t>
+  </si>
+  <si>
+    <t>The 'data' block.</t>
+  </si>
+  <si>
+    <t>A collection of .tf files in a single directory that are used together to create reusable components.</t>
+  </si>
+  <si>
+    <t>How can you pass variables to Terraform at the command line?</t>
+  </si>
+  <si>
+    <t>Using the -var flag (e.g., terraform apply -var="region=us-east-1").</t>
+  </si>
+  <si>
+    <t>What is the purpose of the 'terraform.tfvars' file?</t>
+  </si>
+  <si>
+    <t>It is used to assign values to variables automatically without prompting the user.</t>
+  </si>
+  <si>
+    <t>A way to store the state file outside of your local machine (e.g., S3, Azure Blob Storage) for team collaboration.</t>
+  </si>
+  <si>
+    <t>What is 'State Locking'?</t>
+  </si>
+  <si>
+    <t>A feature that prevents multiple users from modifying the state file simultaneously, avoiding corruption.</t>
+  </si>
+  <si>
+    <t>Which command is used to inspect the current state file in a human-readable format?</t>
+  </si>
+  <si>
+    <t>terraform show</t>
+  </si>
+  <si>
+    <t>A command that reconciles the state file with the actual infrastructure (updates state, doesn't change resources).</t>
+  </si>
+  <si>
+    <t>How do you output a specific value after 'terraform apply'?</t>
+  </si>
+  <si>
+    <t>Using the 'output' block in your configuration.</t>
+  </si>
+  <si>
+    <t>Which command is used to manually mark a resource for recreation?</t>
+  </si>
+  <si>
+    <t>terraform taint (or the newer -replace flag during apply).</t>
+  </si>
+  <si>
+    <t>What is 'HCL'?</t>
+  </si>
+  <si>
+    <t>HashiCorp Configuration Language, the domain-specific language used by Terraform.</t>
+  </si>
+  <si>
+    <t>Which argument is used to make a resource depend on another resource explicitly?</t>
+  </si>
+  <si>
+    <t>depends_on</t>
+  </si>
+  <si>
+    <t>What is the purpose of the 'count' argument?</t>
+  </si>
+  <si>
+    <t>To create multiple instances of a resource or module based on a numeric value.</t>
+  </si>
+  <si>
+    <t>What is 'for_each' used for?</t>
+  </si>
+  <si>
+    <t>To create multiple instances of a resource or module based on a set or map of strings.</t>
+  </si>
+  <si>
+    <t>What are 'Local Values' (locals)?</t>
+  </si>
+  <si>
+    <t>They act like temporary variables to store expressions that you want to reuse within a module.</t>
+  </si>
+  <si>
+    <t>What is the 'terraform console' command used for?</t>
+  </si>
+  <si>
+    <t>It provides an interactive shell to test expressions and functions.</t>
+  </si>
+  <si>
+    <t>Can you use environment variables to set Terraform variable values?</t>
+  </si>
+  <si>
+    <t>Yes, by prefixing the variable name with TF_VAR_ (e.g., TF_VAR_region).</t>
+  </si>
+  <si>
+    <t>What is the 'lifecycle' block used for?</t>
+  </si>
+  <si>
+    <t>To customize the behavior of resource creation, deletion, or updates (e.g., create_before_destroy).</t>
+  </si>
+  <si>
+    <t>Which command is used to download modules defined in your configuration?</t>
+  </si>
+  <si>
+    <t>terraform get (or terraform init).</t>
+  </si>
+  <si>
+    <t>What is a 'Workspace' in Terraform?</t>
+  </si>
+  <si>
+    <t>A way to manage multiple distinct state files for the same configuration (e.g., separate states for staging and production).</t>
+  </si>
+  <si>
+    <t>What is 'Terraform Cloud'?</t>
+  </si>
+  <si>
+    <t>A managed service by HashiCorp that provides remote state storage, execution environments, and policy enforcement.</t>
+  </si>
+  <si>
+    <t>What is 'Sentinel'?</t>
+  </si>
+  <si>
+    <t>A policy-as-code framework used in Terraform Enterprise and Cloud to enforce compliance rules.</t>
+  </si>
+  <si>
+    <t>How do you perform a dry run of 'terraform destroy'?</t>
+  </si>
+  <si>
+    <t>terraform plan -destroy</t>
+  </si>
+  <si>
+    <t>What is the default behavior when terraform apply encounters an error?</t>
+  </si>
+  <si>
+    <t>It stops execution, but any resources already created or modified remain in the state and the infrastructure.</t>
+  </si>
+  <si>
+    <t>Which function is used to read a file's content into a string?</t>
+  </si>
+  <si>
+    <t>file()</t>
+  </si>
+  <si>
+    <t>What is 'terraform import' used for?</t>
+  </si>
+  <si>
+    <t>To bring resources created outside of Terraform under Terraform's management.</t>
+  </si>
+  <si>
+    <t>True or False: The order of resource blocks in a .tf file determines the order of creation.</t>
+  </si>
+  <si>
+    <t>False. Terraform builds a dependency graph and creates resources in the optimal order.</t>
+  </si>
+  <si>
+    <t>What is a 'null_resource'?</t>
+  </si>
+  <si>
+    <t>A resource that implements the standard resource lifecycle but takes no action. Often used with provisioners.</t>
+  </si>
+  <si>
+    <t>Which provisioner is used to run a script on the machine where Terraform is running?</t>
+  </si>
+  <si>
+    <t>local-exec</t>
+  </si>
+  <si>
+    <t>Which provisioner is used to run a script on a remote resource?</t>
+  </si>
+  <si>
+    <t>remote-exec</t>
+  </si>
+  <si>
+    <t>What is 'Terraform Registry'?</t>
+  </si>
+  <si>
+    <t>A central repository for sharing and discovering Terraform providers and modules.</t>
+  </si>
+  <si>
+    <t>How do you reference a variable named 'instance_type' in HCL?</t>
+  </si>
+  <si>
+    <t>var.instance_type</t>
+  </si>
+  <si>
+    <t>Which command is used to see the dependency graph of your resources?</t>
+  </si>
+  <si>
+    <t>terraform graph</t>
+  </si>
+  <si>
+    <t>What is the purpose of the 'ignore_changes' lifecycle argument?</t>
+  </si>
+  <si>
+    <t>To prevent Terraform from trying to revert manual changes made to specific resource attributes outside of Terraform.</t>
+  </si>
+  <si>
+    <t>What is 'Sensitive Data' in Terraform outputs?</t>
+  </si>
+  <si>
+    <t>Outputs marked as 'sensitive = true' are hidden from the console output to protect secrets.</t>
+  </si>
+  <si>
+    <t>Which command is used to move state between different resources or modules?</t>
+  </si>
+  <si>
+    <t>terraform state mv</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -54,7 +664,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,12 +672,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +1039,2224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCA44DC-59A5-4E5B-B422-1D0C0311639D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="6">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="6">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="6">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="6">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="6">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="6">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="6">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="6">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="6">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="6">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="6">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" s="6">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" s="6">
+        <v>56</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="6">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="6">
+        <v>58</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="6">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" s="6">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="6">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" s="6">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" s="6">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="6">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" s="6">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" s="6">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" s="6">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="6">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" s="6">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" s="6">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" s="6">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" s="6">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" s="6">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" s="6">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" s="6">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" s="6">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" s="6">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="6">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" s="6">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" s="6">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" s="6">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" s="6">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" s="6">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" s="6">
+        <v>84</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" s="6">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" s="6">
+        <v>86</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" s="6">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" s="6">
+        <v>88</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" s="6">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" s="6">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" s="6">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" s="6">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" s="6">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" s="6">
+        <v>94</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" s="6">
+        <v>95</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" s="6">
+        <v>96</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" s="6">
+        <v>97</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" s="6">
+        <v>98</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="6">
+        <v>99</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" s="6">
+        <v>100</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" s="6">
+        <v>101</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" s="6">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" s="6">
+        <v>103</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="6">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" s="6">
+        <v>105</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" s="6">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" s="6">
+        <v>107</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" s="6">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" s="6">
+        <v>109</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" s="6">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" s="6">
+        <v>111</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" s="6">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" s="6">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" s="6">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" s="6">
+        <v>115</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" s="6">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" s="6">
+        <v>117</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" s="6">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" s="6">
+        <v>119</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" s="6">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" s="6">
+        <v>121</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" s="6">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" s="6">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" s="6">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" s="6">
+        <v>125</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" s="6">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" s="6">
+        <v>127</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" s="6">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" s="6">
+        <v>129</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" s="6">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" s="6">
+        <v>131</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" s="6">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" s="6">
+        <v>133</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" s="6">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" s="6">
+        <v>135</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" s="6">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" s="6">
+        <v>137</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" s="6">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" s="6">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" s="6">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" s="6">
+        <v>141</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" s="6">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" s="6">
+        <v>143</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" s="6">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" s="6">
+        <v>145</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" s="6">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" s="6">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" s="6">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" s="6">
+        <v>149</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" s="6">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" s="6">
+        <v>151</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" s="6">
+        <v>152</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" s="6">
+        <v>153</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" s="6">
+        <v>154</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" s="6">
+        <v>155</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" s="6">
+        <v>156</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" s="6">
+        <v>157</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" s="6">
+        <v>158</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" s="6">
+        <v>159</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" s="6">
+        <v>160</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" s="6">
+        <v>161</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" s="6">
+        <v>162</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" s="6">
+        <v>163</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" s="6">
+        <v>164</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" s="6">
+        <v>165</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" s="6">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" s="6">
+        <v>167</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A169" s="6">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A170" s="6">
+        <v>169</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A171" s="6">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A172" s="6">
+        <v>171</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A173" s="6">
+        <v>172</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A174" s="6">
+        <v>173</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A175" s="6">
+        <v>174</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A176" s="6">
+        <v>175</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A177" s="6">
+        <v>176</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A178" s="6">
+        <v>177</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A179" s="6">
+        <v>178</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A180" s="6">
+        <v>179</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A181" s="6">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A182" s="6">
+        <v>181</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A183" s="6">
+        <v>182</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A184" s="6">
+        <v>183</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A185" s="6">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A186" s="6">
+        <v>185</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A187" s="6">
+        <v>186</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A188" s="6">
+        <v>187</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A189" s="6">
+        <v>188</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A190" s="6">
+        <v>189</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A191" s="6">
+        <v>190</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A192" s="6">
+        <v>191</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A193" s="6">
+        <v>192</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A194" s="6">
+        <v>193</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A195" s="6">
+        <v>194</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A196" s="6">
+        <v>195</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" s="6">
+        <v>196</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" s="6">
+        <v>197</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" s="6">
+        <v>198</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A200" s="6">
+        <v>199</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A201" s="6">
+        <v>200</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>